--- a/doc/6-3#/点位信息.xlsx
+++ b/doc/6-3#/点位信息.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>设备名称</t>
   </si>
@@ -74,157 +74,166 @@
     <t>采集开始</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>1B22</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>托盘号B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Int16</t>
+  </si>
+  <si>
+    <t>整数</t>
+  </si>
+  <si>
+    <t>型号B</t>
+  </si>
+  <si>
+    <t>屏蔽工位B</t>
+  </si>
+  <si>
+    <t>Int32</t>
+  </si>
+  <si>
+    <t>sting</t>
+  </si>
+  <si>
+    <t>NG代码B</t>
+  </si>
+  <si>
+    <t>A线托盘编号</t>
+  </si>
+  <si>
+    <t>识别代码</t>
+  </si>
+  <si>
+    <t>正游隙检测值</t>
+  </si>
+  <si>
+    <t>({0}/1000)</t>
+  </si>
+  <si>
+    <t>位移量</t>
+  </si>
+  <si>
+    <t>({0}/100)</t>
+  </si>
+  <si>
+    <t>负游隙检测值</t>
+  </si>
+  <si>
+    <t>铆接前成型高度</t>
+  </si>
+  <si>
+    <t>铆接成型力</t>
+  </si>
+  <si>
+    <t>铆接成型位移</t>
+  </si>
+  <si>
+    <t>铆接后成型高度</t>
+  </si>
+  <si>
+    <t>({0}/10000)</t>
+  </si>
+  <si>
+    <t>铆接后成型形状</t>
+  </si>
+  <si>
+    <t>铆接后成型外径</t>
+  </si>
+  <si>
+    <t>密封圈压装压力</t>
+  </si>
+  <si>
+    <t>密封圈压装位移B</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器1</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器2</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器3</t>
+  </si>
+  <si>
+    <t>磁性圈平行差</t>
+  </si>
+  <si>
+    <t>齿圈压装压力</t>
+  </si>
+  <si>
+    <t>齿圈压装位移</t>
+  </si>
+  <si>
+    <t>径跳值</t>
+  </si>
+  <si>
+    <t>端跳值</t>
+  </si>
+  <si>
+    <t>振动下LOAD</t>
+  </si>
+  <si>
+    <t>({0}/10)</t>
+  </si>
+  <si>
+    <t>振动下LH</t>
+  </si>
+  <si>
+    <t>振动下RH</t>
+  </si>
+  <si>
+    <t>振动上LOAD</t>
+  </si>
+  <si>
+    <t>振动上LH</t>
+  </si>
+  <si>
+    <t>振动上RH</t>
+  </si>
+  <si>
+    <t>采集结束</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>Boolean</t>
-  </si>
-  <si>
-    <t>托盘号B</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Int16</t>
-  </si>
-  <si>
-    <t>整数</t>
-  </si>
-  <si>
-    <t>型号B</t>
-  </si>
-  <si>
-    <t>屏蔽工位B</t>
+    <t>防尘盖压装压力</t>
+  </si>
+  <si>
+    <t>防尘盖压装位移</t>
+  </si>
+  <si>
+    <t>扭矩检测值</t>
+  </si>
+  <si>
+    <t>ABS检测峰值</t>
+  </si>
+  <si>
+    <t>ABS检测谷值</t>
+  </si>
+  <si>
+    <t>ABS检测齿数</t>
+  </si>
+  <si>
+    <t>序列码</t>
   </si>
   <si>
     <t>String</t>
   </si>
   <si>
-    <t>sting</t>
-  </si>
-  <si>
-    <t>NG代码B</t>
-  </si>
-  <si>
-    <t>A线托盘编号</t>
-  </si>
-  <si>
-    <t>识别代码</t>
-  </si>
-  <si>
-    <t>Int32</t>
-  </si>
-  <si>
-    <t>正游隙检测值</t>
-  </si>
-  <si>
-    <t>({0}/1000)</t>
-  </si>
-  <si>
-    <t>位移量</t>
-  </si>
-  <si>
-    <t>({0}/100)</t>
-  </si>
-  <si>
-    <t>负游隙检测值</t>
-  </si>
-  <si>
-    <t>铆接前成型高度</t>
-  </si>
-  <si>
-    <t>铆接成型力</t>
-  </si>
-  <si>
-    <t>铆接成型位移</t>
-  </si>
-  <si>
-    <t>铆接后成型高度</t>
-  </si>
-  <si>
-    <t>({0}/10000)</t>
-  </si>
-  <si>
-    <t>铆接后成型形状</t>
-  </si>
-  <si>
-    <t>铆接后成型外径</t>
-  </si>
-  <si>
-    <t>密封圈压装压力</t>
-  </si>
-  <si>
-    <t>密封圈压装位移B</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器1</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器2</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器3</t>
-  </si>
-  <si>
-    <t>磁性圈平行差</t>
-  </si>
-  <si>
-    <t>齿圈压装压力</t>
-  </si>
-  <si>
-    <t>齿圈压装位移</t>
-  </si>
-  <si>
-    <t>径跳值</t>
-  </si>
-  <si>
-    <t>端跳值</t>
-  </si>
-  <si>
-    <t>振动下LOAD</t>
-  </si>
-  <si>
-    <t>({0}/10)</t>
-  </si>
-  <si>
-    <t>振动下LH</t>
-  </si>
-  <si>
-    <t>振动下RH</t>
-  </si>
-  <si>
-    <t>振动上LOAD</t>
-  </si>
-  <si>
-    <t>振动上LH</t>
-  </si>
-  <si>
-    <t>振动上RH</t>
-  </si>
-  <si>
-    <t>采集结束</t>
-  </si>
-  <si>
-    <t>防尘盖压装压力</t>
-  </si>
-  <si>
-    <t>防尘盖压装位移</t>
-  </si>
-  <si>
-    <t>扭矩检测值</t>
-  </si>
-  <si>
-    <t>ABS检测峰值</t>
-  </si>
-  <si>
-    <t>ABS检测谷值</t>
-  </si>
-  <si>
-    <t>ABS检测齿数</t>
-  </si>
-  <si>
-    <t>二维码打标内容</t>
+    <t>半成品码</t>
   </si>
   <si>
     <t>A线</t>
@@ -1330,8 +1339,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O63"/>
+  <sheetPr/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1383,7 +1392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="14.25" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1400,11 +1409,11 @@
       <c r="F2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="8">
-        <v>3300</v>
+      <c r="G2" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -1422,24 +1431,24 @@
         <v>2000</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="9">
         <v>13000</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:12">
@@ -1453,24 +1462,24 @@
         <v>2000</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="9">
         <v>13001</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
       </c>
       <c r="J4" s="10"/>
       <c r="L4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:12">
@@ -1484,24 +1493,24 @@
         <v>2000</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3">
         <v>13002</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>22</v>
+      <c r="H5" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="I5" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="10"/>
       <c r="L5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:12">
@@ -1515,24 +1524,24 @@
         <v>2000</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3">
         <v>13004</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>22</v>
+      <c r="H6" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="I6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="10"/>
       <c r="L6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:12">
@@ -1546,24 +1555,24 @@
         <v>2000</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="9">
         <v>13005</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="9">
         <v>1</v>
       </c>
       <c r="J7" s="10"/>
       <c r="L7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:12">
@@ -1577,24 +1586,24 @@
         <v>2000</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="9">
         <v>13006</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
       </c>
       <c r="J8" s="10"/>
       <c r="L8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:12">
@@ -1612,13 +1621,13 @@
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="9">
         <v>13009</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I9" s="9">
         <v>1</v>
@@ -1645,13 +1654,13 @@
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" s="9">
         <v>13011</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I10" s="9">
         <v>1</v>
@@ -1678,13 +1687,13 @@
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="9">
         <v>13013</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
@@ -1711,13 +1720,13 @@
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="9">
         <v>13015</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
@@ -1744,20 +1753,20 @@
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="9">
         <v>13017</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
       </c>
       <c r="J13" s="10"/>
       <c r="L13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:12">
@@ -1775,13 +1784,13 @@
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="9">
         <v>13019</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
@@ -1808,13 +1817,13 @@
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="9">
         <v>13021</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I15" s="9">
         <v>1</v>
@@ -1841,13 +1850,13 @@
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="9">
         <v>13023</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I16" s="9">
         <v>1</v>
@@ -1874,13 +1883,13 @@
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="9">
         <v>13025</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I17" s="9">
         <v>1</v>
@@ -1907,13 +1916,13 @@
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="9">
         <v>13027</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
@@ -1940,13 +1949,13 @@
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="9">
         <v>13029</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
@@ -1973,13 +1982,13 @@
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="9">
         <v>13034</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
@@ -2006,13 +2015,13 @@
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" s="9">
         <v>13037</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21" s="9">
         <v>1</v>
@@ -2039,13 +2048,13 @@
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" s="9">
         <v>13040</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="9">
         <v>1</v>
@@ -2072,13 +2081,13 @@
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" s="9">
         <v>13043</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I23" s="9">
         <v>1</v>
@@ -2105,13 +2114,13 @@
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G24" s="9">
         <v>13045</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I24" s="9">
         <v>1</v>
@@ -2138,13 +2147,13 @@
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="9">
         <v>13047</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I25" s="9">
         <v>1</v>
@@ -2171,13 +2180,13 @@
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" s="9">
         <v>13067</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I26" s="9">
         <v>1</v>
@@ -2204,13 +2213,13 @@
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="9">
         <v>13069</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I27" s="9">
         <v>1</v>
@@ -2237,13 +2246,13 @@
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" s="9">
         <v>13073</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I28" s="9">
         <v>1</v>
@@ -2270,13 +2279,13 @@
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="9">
         <v>13075</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I29" s="9">
         <v>1</v>
@@ -2303,13 +2312,13 @@
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" s="9">
         <v>13077</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I30" s="9">
         <v>1</v>
@@ -2336,13 +2345,13 @@
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31" s="9">
         <v>13079</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I31" s="9">
         <v>1</v>
@@ -2369,13 +2378,13 @@
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" s="9">
         <v>13081</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I32" s="9">
         <v>1</v>
@@ -2402,13 +2411,13 @@
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" s="9">
         <v>13083</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I33" s="9">
         <v>1</v>
@@ -2435,13 +2444,13 @@
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G34" s="8">
         <v>3301</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I34" s="14">
         <v>1</v>
@@ -2460,17 +2469,17 @@
         <v>2000</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" s="9">
         <v>13085</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I35" s="9">
         <v>1</v>
@@ -2493,17 +2502,17 @@
         <v>2000</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G36" s="9">
         <v>13087</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I36" s="9">
         <v>1</v>
@@ -2526,17 +2535,17 @@
         <v>2000</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="9">
         <v>13091</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I37" s="9">
         <v>1</v>
@@ -2559,17 +2568,17 @@
         <v>2000</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G38" s="9">
         <v>13093</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I38" s="9">
         <v>1</v>
@@ -2592,24 +2601,24 @@
         <v>2000</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39" s="9">
         <v>13095</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I39" s="9">
         <v>1</v>
       </c>
       <c r="J39" s="10"/>
       <c r="L39" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" ht="14.25" spans="1:15">
@@ -2623,17 +2632,17 @@
         <v>2000</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G40" s="9">
         <v>13097</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I40" s="9">
         <v>1</v>
@@ -2651,163 +2660,154 @@
         <v>2000</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41" s="14"/>
       <c r="F41" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G41" s="9">
-        <v>13099</v>
+        <v>4704</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I41" s="9">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J41" s="15"/>
       <c r="L41" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
-      <c r="A42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="8">
-        <v>6000</v>
+    </row>
+    <row r="42" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A42" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="14">
+        <v>2000</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G42" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="8">
-        <v>1</v>
+        <v>5400</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42" s="9">
+        <v>20</v>
       </c>
       <c r="J42" s="10"/>
-      <c r="L42" s="12"/>
-    </row>
-    <row r="43" ht="14.25" hidden="1" spans="1:15">
+      <c r="L42" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A43" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C43" s="8">
         <v>6000</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>67</v>
+      <c r="D43" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E43" s="8"/>
-      <c r="F43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="9">
-        <v>12400</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="9">
-        <v>1</v>
-      </c>
-      <c r="J43" s="18"/>
-      <c r="L43" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" hidden="1" spans="1:15">
+      <c r="F43" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="8">
+        <v>1</v>
+      </c>
+      <c r="J43" s="10"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" ht="14.25" spans="1:15">
       <c r="A44" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C44" s="8">
         <v>6000</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G44" s="9">
-        <v>12401</v>
+        <v>12400</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I44" s="9">
         <v>1</v>
       </c>
-      <c r="J44" s="10"/>
+      <c r="J44" s="18"/>
       <c r="L44" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" hidden="1" spans="1:15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" spans="1:15">
       <c r="A45" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C45" s="8">
         <v>6000</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G45" s="9">
-        <v>12402</v>
+        <v>12401</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I45" s="9">
-        <v>4</v>
-      </c>
-      <c r="J45" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="J45" s="10"/>
       <c r="L45" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M45">
-        <v>18</v>
-      </c>
-      <c r="N45" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" hidden="1" spans="1:15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" spans="1:15">
       <c r="A46" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C46" s="8">
         <v>6000</v>
@@ -2817,86 +2817,93 @@
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G46" s="9">
-        <v>12404</v>
+        <v>12402</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I46" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="19"/>
       <c r="L46" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M46">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" hidden="1" spans="1:15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" spans="1:15">
       <c r="A47" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C47" s="8">
         <v>6000</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G47" s="9">
-        <v>12405</v>
+        <v>12404</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" s="9">
         <v>1</v>
       </c>
-      <c r="J47" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" hidden="1" spans="1:15">
+      <c r="J47" s="19"/>
+      <c r="L47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M47">
+        <v>32</v>
+      </c>
+      <c r="N47" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" spans="1:15">
       <c r="A48" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C48" s="8">
         <v>6000</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G48" s="9">
-        <v>12406</v>
+        <v>12405</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48" s="9">
         <v>1</v>
@@ -2908,28 +2915,28 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="49" ht="14.25" hidden="1" spans="1:12">
+    <row r="49" ht="14.25" spans="1:12">
       <c r="A49" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C49" s="8">
         <v>6000</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" s="9">
-        <v>12407</v>
+        <v>12406</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="9">
         <v>1</v>
@@ -2941,156 +2948,156 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="50" ht="14.25" hidden="1" spans="1:12">
+    <row r="50" ht="14.25" spans="1:12">
       <c r="A50" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C50" s="8">
         <v>6000</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50" s="9">
-        <v>12408</v>
+        <v>12407</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" s="9">
         <v>1</v>
       </c>
-      <c r="J50" s="10"/>
-      <c r="L50" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" hidden="1" spans="1:12">
+      <c r="J50" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" spans="1:12">
       <c r="A51" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C51" s="8">
         <v>6000</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G51" s="9">
-        <v>12409</v>
+        <v>12408</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I51" s="9">
         <v>1</v>
       </c>
       <c r="J51" s="10"/>
       <c r="L51" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" hidden="1" spans="1:12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" spans="1:12">
       <c r="A52" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C52" s="8">
         <v>6000</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G52" s="9">
-        <v>12412</v>
+        <v>12409</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" s="9">
         <v>1</v>
       </c>
-      <c r="J52" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" hidden="1" spans="1:12">
+      <c r="J52" s="10"/>
+      <c r="L52" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" spans="1:12">
       <c r="A53" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C53" s="8">
         <v>6000</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G53" s="9">
-        <v>12416</v>
+        <v>12412</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I53" s="9">
         <v>1</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L53" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25" hidden="1" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" spans="1:12">
       <c r="A54" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C54" s="8">
         <v>6000</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G54" s="9">
-        <v>12418</v>
+        <v>12416</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I54" s="9">
         <v>1</v>
@@ -3102,28 +3109,28 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" ht="14.25" hidden="1" spans="1:12">
+    <row r="55" ht="14.25" spans="1:12">
       <c r="A55" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C55" s="8">
         <v>6000</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G55" s="9">
-        <v>12432</v>
+        <v>12418</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I55" s="9">
         <v>1</v>
@@ -3135,94 +3142,94 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="56" ht="14.25" hidden="1" spans="1:12">
+    <row r="56" ht="14.25" spans="1:12">
       <c r="A56" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C56" s="8">
         <v>6000</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G56" s="9">
-        <v>12435</v>
+        <v>12432</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I56" s="9">
         <v>1</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L56" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25" hidden="1" spans="1:12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25" spans="1:12">
       <c r="A57" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C57" s="8">
         <v>6000</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G57" s="9">
-        <v>12437</v>
+        <v>12435</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I57" s="9">
         <v>1</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L57" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" hidden="1" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" spans="1:12">
       <c r="A58" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C58" s="8">
         <v>6000</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G58" s="9">
-        <v>12439</v>
+        <v>12437</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I58" s="9">
         <v>1</v>
@@ -3234,30 +3241,30 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="59" ht="14.25" hidden="1" spans="1:12">
+    <row r="59" ht="14.25" spans="1:12">
       <c r="A59" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C59" s="8">
         <v>6000</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>85</v>
+      <c r="D59" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="E59" s="8"/>
-      <c r="F59" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="8">
-        <v>12453</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="F59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="9">
+        <v>12439</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="9">
         <v>1</v>
       </c>
       <c r="J59" s="10" t="s">
@@ -3267,122 +3274,122 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="60" ht="14.25" hidden="1" spans="1:12">
-      <c r="A60" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" s="20">
+    <row r="60" ht="14.25" spans="1:12">
+      <c r="A60" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="8">
         <v>6000</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="8">
+        <v>12453</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="8">
+        <v>1</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" spans="1:12">
+      <c r="A61" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="20">
+        <v>6000</v>
+      </c>
+      <c r="D61" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="20">
+      <c r="E61" s="20"/>
+      <c r="F61" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G61" s="20">
         <v>2501</v>
       </c>
-      <c r="H60" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="20">
-        <v>1</v>
-      </c>
-      <c r="J60" s="18"/>
-    </row>
-    <row r="61" ht="14.25" hidden="1" spans="1:12">
-      <c r="A61" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61" s="8">
-        <v>6000</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="9">
-        <v>12457</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I61" s="9">
-        <v>1</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L61" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" ht="14.25" hidden="1" spans="1:12">
+      <c r="H61" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="20">
+        <v>1</v>
+      </c>
+      <c r="J61" s="18"/>
+    </row>
+    <row r="62" ht="14.25" spans="1:12">
       <c r="A62" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C62" s="8">
         <v>6000</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G62" s="9">
-        <v>12461</v>
+        <v>12457</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I62" s="9">
         <v>1</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L62" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" spans="1:12">
       <c r="A63" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C63" s="8">
         <v>6000</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G63" s="9">
-        <v>12463</v>
+        <v>12461</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I63" s="9">
         <v>1</v>
@@ -3394,13 +3401,41 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="64" s="2" customFormat="1" ht="14.25" spans="1:12">
+      <c r="A64" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="8">
+        <v>12463</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="8">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L64" s="3">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O63" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="B线"/>
-      </customFilters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:L63">
@@ -3409,13 +3444,13 @@
   <conditionalFormatting sqref="D2">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41">
+  <conditionalFormatting sqref="D43">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D42">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D40 D43:D1048576">
+  <conditionalFormatting sqref="D1 D3:D40 D44:D63 D65:D1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
